--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3234" yWindow="3234" windowWidth="17280" windowHeight="9984" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="FANT26 merged" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -414,7 +413,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA16E05-9FAF-440C-B6AC-B2D25BD2C1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0FF234-E361-4518-BAA3-65CBB755E06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3234" yWindow="3234" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FANT26 merged" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="124">
   <si>
     <t>Zeitstempel</t>
   </si>
@@ -199,12 +199,6 @@
     <t>2026/05/15 11:28:19 AM OESZ</t>
   </si>
   <si>
-    <t>Obeng Mensah &amp; Fäder</t>
-  </si>
-  <si>
-    <t>Deborah &amp; Eymard</t>
-  </si>
-  <si>
     <t>University of Cologne</t>
   </si>
   <si>
@@ -378,6 +372,30 @@
   </si>
   <si>
     <t>Archaeological research in Egypt’s desert regions has faced significant challenges in recent years due to regional and global constraints. Despite these difficulties, close collaboration with local partners has enabled joint initiatives in both research and academic training. This contribution provides an overview of archaeological projects and activities conducted by the University of Cologne in the Western Desert of Egypt over the past years and discusses future perspectives.</t>
+  </si>
+  <si>
+    <t>Gestrich</t>
+  </si>
+  <si>
+    <t>Nick</t>
+  </si>
+  <si>
+    <t>New archaeological fieldwork in the Tagant, Mauritania: The end of the Tichitt tradition?</t>
+  </si>
+  <si>
+    <t>Puerta Schardt</t>
+  </si>
+  <si>
+    <t>Juan-Marco</t>
+  </si>
+  <si>
+    <t>Provenance analysis of clay smoking pipes in West Africa using pXRF</t>
+  </si>
+  <si>
+    <t>The Late Stone Age Tichitt complex is famous (among archaeologists of West Africa, at least) for its early and large stone-built settlements, indications of social complexity, and settled agro-pastoral lifeways. At the same time, research has been rather sparsely spread over its large, densely settled area. Many of the key questions remain essentially unanswered. The Tagant, to the west of the Tichitt complex' core area, is often cited as having continued the Tichitt tradition beyond its end in the mid-first millennium BCE. However, the entire region has only been subject of fieldwork for a single PhD thesis in the early 1990s. Since then, satellite surveys have been carried out, which provide only limited information. This paper reports on first results of a restudy of materials and a short survey campaign, as well as giving a preview of future planned work.</t>
+  </si>
+  <si>
+    <t>Obeng Mensah, Deborah &amp; Fäder, Eymard</t>
   </si>
 </sst>
 </file>
@@ -717,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -951,19 +969,16 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
         <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
@@ -972,42 +987,42 @@
         <v>21</v>
       </c>
       <c r="N6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P6" t="s">
         <v>62</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" t="s">
         <v>63</v>
       </c>
-      <c r="P6" t="s">
+      <c r="R6" t="s">
         <v>64</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="S6" t="s">
         <v>65</v>
-      </c>
-      <c r="R6" t="s">
-        <v>66</v>
-      </c>
-      <c r="S6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
         <v>68</v>
-      </c>
-      <c r="B7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>70</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
         <v>20</v>
@@ -1016,170 +1031,170 @@
         <v>21</v>
       </c>
       <c r="N7" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R7" t="s">
         <v>73</v>
       </c>
-      <c r="O7" t="s">
+      <c r="S7" t="s">
         <v>74</v>
-      </c>
-      <c r="R7" t="s">
-        <v>75</v>
-      </c>
-      <c r="S7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
         <v>77</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
       </c>
       <c r="D8" t="s">
         <v>49</v>
       </c>
       <c r="E8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" t="s">
         <v>80</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>81</v>
       </c>
-      <c r="G8" t="s">
+      <c r="N8" t="s">
         <v>82</v>
       </c>
-      <c r="H8" t="s">
+      <c r="O8" t="s">
         <v>83</v>
       </c>
-      <c r="N8" t="s">
+      <c r="R8" t="s">
         <v>84</v>
       </c>
-      <c r="O8" t="s">
+      <c r="S8" t="s">
         <v>85</v>
-      </c>
-      <c r="R8" t="s">
-        <v>86</v>
-      </c>
-      <c r="S8" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
         <v>88</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>89</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>90</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>91</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" t="s">
+        <v>81</v>
+      </c>
+      <c r="N9" t="s">
         <v>92</v>
       </c>
-      <c r="F9" t="s">
+      <c r="O9" t="s">
         <v>93</v>
       </c>
-      <c r="G9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" t="s">
-        <v>83</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="R9" t="s">
         <v>94</v>
       </c>
-      <c r="O9" t="s">
+      <c r="S9" t="s">
         <v>95</v>
-      </c>
-      <c r="R9" t="s">
-        <v>96</v>
-      </c>
-      <c r="S9" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" t="s">
         <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" t="s">
-        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
         <v>44</v>
       </c>
       <c r="I10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" t="s">
         <v>103</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>104</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>106</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s">
         <v>44</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
         <v>110</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" t="s">
-        <v>112</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -1188,25 +1203,74 @@
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N12" t="s">
+        <v>112</v>
+      </c>
+      <c r="O12" t="s">
+        <v>113</v>
+      </c>
+      <c r="R12" t="s">
         <v>114</v>
       </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>115</v>
       </c>
-      <c r="R12" t="s">
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" t="s">
         <v>116</v>
       </c>
-      <c r="S12" t="s">
+      <c r="C13" t="s">
         <v>117</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s">
+        <v>118</v>
+      </c>
+      <c r="S13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3234" yWindow="3234" windowWidth="17280" windowHeight="9984" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="9984" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="FANT26 merged" sheetId="1" state="visible" r:id="rId1"/>
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -780,12 +780,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Obeng Mensah &amp; Fäder</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Deborah &amp; Eymard</t>
+          <t>Obeng Mensah, Deborah &amp; Fäder, Eymard</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1171,6 +1166,85 @@
       <c r="S12" t="inlineStr">
         <is>
           <t>Archaeological research in Egypt’s desert regions has faced significant challenges in recent years due to regional and global constraints. Despite these difficulties, close collaboration with local partners has enabled joint initiatives in both research and academic training. This contribution provides an overview of archaeological projects and activities conducted by the University of Cologne in the Western Desert of Egypt over the past years and discusses future perspectives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gestrich</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Goethe Universität Frankfurt</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>New archaeological fieldwork in the Tagant, Mauritania: The end of the Tichitt tradition?</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>The Late Stone Age Tichitt complex is famous (among archaeologists of West Africa, at least) for its early and large stone-built settlements, indications of social complexity, and settled agro-pastoral lifeways. At the same time, research has been rather sparsely spread over its large, densely settled area. Many of the key questions remain essentially unanswered. The Tagant, to the west of the Tichitt complex' core area, is often cited as having continued the Tichitt tradition beyond its end in the mid-first millennium BCE. However, the entire region has only been subject of fieldwork for a single PhD thesis in the early 1990s. Since then, satellite surveys have been carried out, which provide only limited information. This paper reports on first results of a restudy of materials and a short survey campaign, as well as giving a preview of future planned work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Puerta Schardt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Juan-Marco</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Doctoral candidate</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Goethe Universität Frankfurt</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Provenance analysis of clay smoking pipes in West Africa using pXRF</t>
         </is>
       </c>
     </row>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0FF234-E361-4518-BAA3-65CBB755E06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E98C26A-33DD-4B42-970F-904F9A2DBA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="124">
   <si>
     <t>Zeitstempel</t>
   </si>
@@ -1225,6 +1225,9 @@
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>108</v>
+      </c>
       <c r="B13" t="s">
         <v>116</v>
       </c>
@@ -1251,6 +1254,9 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>108</v>
+      </c>
       <c r="B14" t="s">
         <v>119</v>
       </c>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -1170,6 +1170,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026/05/16 1:24:35 AM OESZ</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Gestrich</t>
@@ -1212,6 +1217,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026/05/16 1:24:35 AM OESZ</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Puerta Schardt</t>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E98C26A-33DD-4B42-970F-904F9A2DBA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2ADACBD-0C33-4DAB-A299-189E1C1F49EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="126">
   <si>
     <t>Zeitstempel</t>
   </si>
@@ -396,6 +396,12 @@
   </si>
   <si>
     <t>Obeng Mensah, Deborah &amp; Fäder, Eymard</t>
+  </si>
+  <si>
+    <t>From around 1600 CE, clay smoking pipes become a regular component of West African site assemblages, yet they routinely differ from the accompanying pottery in both fabric and decoration. We apply pXRF to pipes and local pottery from 5 different sites, using the potteries geochemical signature as a baseline against which pipe provenance can be assessed to get a better inside on the relation between pipe and pottery production.</t>
+  </si>
+  <si>
+    <t>Mauretania, Tichitt, Tagant, Settlements, Agropastoralism</t>
   </si>
 </sst>
 </file>
@@ -431,8 +437,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1249,6 +1258,9 @@
       <c r="N13" t="s">
         <v>118</v>
       </c>
+      <c r="R13" t="s">
+        <v>125</v>
+      </c>
       <c r="S13" t="s">
         <v>122</v>
       </c>
@@ -1278,8 +1290,12 @@
       <c r="N14" t="s">
         <v>121</v>
       </c>
+      <c r="S14" s="1" t="s">
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -45,8 +45,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1210,6 +1213,11 @@
           <t>New archaeological fieldwork in the Tagant, Mauritania: The end of the Tichitt tradition?</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Mauretania, Tichitt, Tagant, Settlements, Agropastoralism</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
           <t>The Late Stone Age Tichitt complex is famous (among archaeologists of West Africa, at least) for its early and large stone-built settlements, indications of social complexity, and settled agro-pastoral lifeways. At the same time, research has been rather sparsely spread over its large, densely settled area. Many of the key questions remain essentially unanswered. The Tagant, to the west of the Tichitt complex' core area, is often cited as having continued the Tichitt tradition beyond its end in the mid-first millennium BCE. However, the entire region has only been subject of fieldwork for a single PhD thesis in the early 1990s. Since then, satellite surveys have been carried out, which provide only limited information. This paper reports on first results of a restudy of materials and a short survey campaign, as well as giving a preview of future planned work.</t>
@@ -1257,8 +1265,14 @@
           <t>Provenance analysis of clay smoking pipes in West Africa using pXRF</t>
         </is>
       </c>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t>From around 1600 CE, clay smoking pipes become a regular component of West African site assemblages, yet they routinely differ from the accompanying pottery in both fabric and decoration. We apply pXRF to pipes and local pottery from 5 different sites, using the potteries geochemical signature as a baseline against which pipe provenance can be assessed to get a better inside on the relation between pipe and pottery production.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2ADACBD-0C33-4DAB-A299-189E1C1F49EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3825E419-F001-4B48-8414-E040BDDAFEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="128">
   <si>
     <t>Zeitstempel</t>
   </si>
@@ -211,12 +211,6 @@
     <t>Deborah Obeng Mensah, Eymard Fäder</t>
   </si>
   <si>
-    <t>Deborah Obeng Mensah</t>
-  </si>
-  <si>
-    <t>Eymard Fäder</t>
-  </si>
-  <si>
     <t>3D imaging, digital archives, cultural heritage preservation</t>
   </si>
   <si>
@@ -402,6 +396,18 @@
   </si>
   <si>
     <t>Mauretania, Tichitt, Tagant, Settlements, Agropastoralism</t>
+  </si>
+  <si>
+    <t>Patrick Quinn</t>
+  </si>
+  <si>
+    <t>Roundtable</t>
+  </si>
+  <si>
+    <t>Archaeometrical methods in African archaoelogy</t>
+  </si>
+  <si>
+    <t>Archaeometric methods play an increasingly important role in African archaeology, allowing us to extract from archaeological materials a wealth of information on knowledge and skills, trade, and use that is not accessible to the naked eye. These methods differ considerably in terms of effort and the insights they yield. What they share, however, is the need for the research question, sampling strategy, data management, and data analysis to be carefully considered and aligned with one another.This roundtable offers an overview of different archaeometric approaches and a discussion of their opportunities and challenges. Which archaeometric questions and methods are currently relevant? What resources and capacities do we have, and how can we expand or connect them? How can archaeometric projects be designed together with African partners?</t>
   </si>
 </sst>
 </file>
@@ -744,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -978,7 +984,7 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
         <v>41</v>
@@ -1001,37 +1007,31 @@
       <c r="O6" t="s">
         <v>61</v>
       </c>
-      <c r="P6" t="s">
+      <c r="R6" t="s">
         <v>62</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="S6" t="s">
         <v>63</v>
-      </c>
-      <c r="R6" t="s">
-        <v>64</v>
-      </c>
-      <c r="S6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
         <v>66</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
         <v>20</v>
@@ -1040,170 +1040,170 @@
         <v>21</v>
       </c>
       <c r="N7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R7" t="s">
         <v>71</v>
       </c>
-      <c r="O7" t="s">
+      <c r="S7" t="s">
         <v>72</v>
-      </c>
-      <c r="R7" t="s">
-        <v>73</v>
-      </c>
-      <c r="S7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>77</v>
       </c>
       <c r="D8" t="s">
         <v>49</v>
       </c>
       <c r="E8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s">
         <v>78</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>79</v>
       </c>
-      <c r="G8" t="s">
+      <c r="N8" t="s">
         <v>80</v>
       </c>
-      <c r="H8" t="s">
+      <c r="O8" t="s">
         <v>81</v>
       </c>
-      <c r="N8" t="s">
+      <c r="R8" t="s">
         <v>82</v>
       </c>
-      <c r="O8" t="s">
+      <c r="S8" t="s">
         <v>83</v>
-      </c>
-      <c r="R8" t="s">
-        <v>84</v>
-      </c>
-      <c r="S8" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
         <v>86</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>87</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>88</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>89</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9" t="s">
         <v>90</v>
       </c>
-      <c r="F9" t="s">
+      <c r="O9" t="s">
         <v>91</v>
       </c>
-      <c r="G9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" t="s">
-        <v>81</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="R9" t="s">
         <v>92</v>
       </c>
-      <c r="O9" t="s">
+      <c r="S9" t="s">
         <v>93</v>
-      </c>
-      <c r="R9" t="s">
-        <v>94</v>
-      </c>
-      <c r="S9" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
         <v>96</v>
-      </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" t="s">
-        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s">
         <v>44</v>
       </c>
       <c r="I10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" t="s">
         <v>101</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>102</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
         <v>44</v>
       </c>
       <c r="I11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" t="s">
         <v>108</v>
-      </c>
-      <c r="B12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" t="s">
-        <v>110</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -1212,42 +1212,42 @@
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N12" t="s">
+        <v>110</v>
+      </c>
+      <c r="O12" t="s">
+        <v>111</v>
+      </c>
+      <c r="R12" t="s">
         <v>112</v>
       </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>113</v>
-      </c>
-      <c r="R12" t="s">
-        <v>114</v>
-      </c>
-      <c r="S12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
         <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
         <v>20</v>
@@ -1256,30 +1256,30 @@
         <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="R13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="S13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
         <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s">
         <v>20</v>
@@ -1288,10 +1288,33 @@
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="P14" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>124</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>125</v>
+      </c>
+      <c r="T15" t="s">
+        <v>126</v>
+      </c>
+      <c r="X15" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -817,16 +817,6 @@
           <t>Deborah Obeng Mensah, Eymard Fäder</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Deborah Obeng Mensah</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Eymard Fäder</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>3D imaging, digital archives, cultural heritage preservation</t>
@@ -1265,9 +1255,46 @@
           <t>Provenance analysis of clay smoking pipes in West Africa using pXRF</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Umar Musa</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Patrick Quinn</t>
+        </is>
+      </c>
       <c r="S14" s="1" t="inlineStr">
         <is>
           <t>From around 1600 CE, clay smoking pipes become a regular component of West African site assemblages, yet they routinely differ from the accompanying pottery in both fabric and decoration. We apply pXRF to pipes and local pottery from 5 different sites, using the potteries geochemical signature as a baseline against which pipe provenance can be assessed to get a better inside on the relation between pipe and pottery production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Goethe Universität Frankfurt</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Roundtable</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Archaeometrical methods in African archaoelogy</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Archaeometric methods play an increasingly important role in African archaeology, allowing us to extract from archaeological materials a wealth of information on knowledge and skills, trade, and use that is not accessible to the naked eye. These methods differ considerably in terms of effort and the insights they yield. What they share, however, is the need for the research question, sampling strategy, data management, and data analysis to be carefully considered and aligned with one another.This roundtable offers an overview of different archaeometric approaches and a discussion of their opportunities and challenges. Which archaeometric questions and methods are currently relevant? What resources and capacities do we have, and how can we expand or connect them? How can archaeometric projects be designed together with African partners?</t>
         </is>
       </c>
     </row>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3825E419-F001-4B48-8414-E040BDDAFEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A9F131-F52E-4072-97BD-8EE593A4D833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="3600" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FANT26 merged" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="138">
   <si>
     <t>Zeitstempel</t>
   </si>
@@ -408,6 +409,36 @@
   </si>
   <si>
     <t>Archaeometric methods play an increasingly important role in African archaeology, allowing us to extract from archaeological materials a wealth of information on knowledge and skills, trade, and use that is not accessible to the naked eye. These methods differ considerably in terms of effort and the insights they yield. What they share, however, is the need for the research question, sampling strategy, data management, and data analysis to be carefully considered and aligned with one another.This roundtable offers an overview of different archaeometric approaches and a discussion of their opportunities and challenges. Which archaeometric questions and methods are currently relevant? What resources and capacities do we have, and how can we expand or connect them? How can archaeometric projects be designed together with African partners?</t>
+  </si>
+  <si>
+    <t>Höhn</t>
+  </si>
+  <si>
+    <t>Alexa</t>
+  </si>
+  <si>
+    <t>Die archäobotanischen Vergleichssammlungen an der Goethe-Universität, Frankfurt am Main</t>
+  </si>
+  <si>
+    <t>Vergleichssammlungen sind eine unverzichtbare Grundlage in archäobotanischer Forschung und Lehre. An der Goethe-Universität umfassen sie Hölzer, Pollen, Früchte, Samen und Phytolithen. Insbesondere die umfangreichen westafrikanischen Bestände stellen eine international bedeutende Ressource dar und werden regelmäßig von Gastwissenschaftlerinnen und Gastwissenschaftlern genutzt. Im Rahmen der Objektdatenbank CODA werden die Sammlungen systematisch digital erschlossen, um ihre wissenschaftliche Nutzung weltweit zu erleichtern. Zugleich dokumentieren die Objekte Umwelt, Kultur- und Kolonialgeschichte und besitzen damit einen eigenständigen Quellenwert für interdisziplinäre Forschung.</t>
+  </si>
+  <si>
+    <t>Sammlungen, Westafrika, Archäobotanik</t>
+  </si>
+  <si>
+    <t>Magnavita</t>
+  </si>
+  <si>
+    <t>Sonja</t>
+  </si>
+  <si>
+    <t>Trans-Sudanic vs. Trans-Saharan contacts: chemical analysis of glass beads from Kanem, Chad</t>
+  </si>
+  <si>
+    <t>This talk presents the results of archaeometric analyses of a collection of 12th-14th century glass beads from the archaeological site of Tié (Chad) — the presumed capital of the early Kanem Empire northeast of Lake Chad. The appearance, manufacture, and chemical composition of the beads largely correspond to those of glass beads that were in circulation in the Indian Ocean region, suggesting a connection between Kanem and East or Northeast Africa. In light of the finds from Kanem, a trade route along the savanna belt seems more plausible than a trans-Saharan route, especially when other glass bead finds from the continent are taken into account as well.</t>
+  </si>
+  <si>
+    <t>glass, beads, Kanem, archaeometry</t>
   </si>
 </sst>
 </file>
@@ -750,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1301,6 +1332,9 @@
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>106</v>
+      </c>
       <c r="E15" t="s">
         <v>76</v>
       </c>
@@ -1315,6 +1349,67 @@
       </c>
       <c r="X15" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s">
+        <v>79</v>
+      </c>
+      <c r="N16" t="s">
+        <v>130</v>
+      </c>
+      <c r="R16" t="s">
+        <v>132</v>
+      </c>
+      <c r="S16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" t="s">
+        <v>135</v>
+      </c>
+      <c r="R17" t="s">
+        <v>137</v>
+      </c>
+      <c r="S17" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3264" yWindow="3264" windowWidth="17280" windowHeight="9984" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3600" yWindow="3600" windowWidth="17280" windowHeight="9984" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="FANT26 merged" sheetId="1" state="visible" r:id="rId1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -1272,6 +1272,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026/05/16 1:24:35 AM OESZ</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Goethe Universität Frankfurt</t>
@@ -1295,6 +1300,105 @@
       <c r="X15" t="inlineStr">
         <is>
           <t>Archaeometric methods play an increasingly important role in African archaeology, allowing us to extract from archaeological materials a wealth of information on knowledge and skills, trade, and use that is not accessible to the naked eye. These methods differ considerably in terms of effort and the insights they yield. What they share, however, is the need for the research question, sampling strategy, data management, and data analysis to be carefully considered and aligned with one another.This roundtable offers an overview of different archaeometric approaches and a discussion of their opportunities and challenges. Which archaeometric questions and methods are currently relevant? What resources and capacities do we have, and how can we expand or connect them? How can archaeometric projects be designed together with African partners?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026/05/16 1:24:35 AM OESZ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Höhn</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Alexa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Goethe Universität Frankfurt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Präsentation</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Die archäobotanischen Vergleichssammlungen an der Goethe-Universität, Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Sammlungen, Westafrika, Archäobotanik</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Vergleichssammlungen sind eine unverzichtbare Grundlage in archäobotanischer Forschung und Lehre. An der Goethe-Universität umfassen sie Hölzer, Pollen, Früchte, Samen und Phytolithen. Insbesondere die umfangreichen westafrikanischen Bestände stellen eine international bedeutende Ressource dar und werden regelmäßig von Gastwissenschaftlerinnen und Gastwissenschaftlern genutzt. Im Rahmen der Objektdatenbank CODA werden die Sammlungen systematisch digital erschlossen, um ihre wissenschaftliche Nutzung weltweit zu erleichtern. Zugleich dokumentieren die Objekte Umwelt, Kultur- und Kolonialgeschichte und besitzen damit einen eigenständigen Quellenwert für interdisziplinäre Forschung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Magnavita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sonja</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Goethe Universität Frankfurt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Trans-Sudanic vs. Trans-Saharan contacts: chemical analysis of glass beads from Kanem, Chad</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>glass, beads, Kanem, archaeometry</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>This talk presents the results of archaeometric analyses of a collection of 12th-14th century glass beads from the archaeological site of Tié (Chad) — the presumed capital of the early Kanem Empire northeast of Lake Chad. The appearance, manufacture, and chemical composition of the beads largely correspond to those of glass beads that were in circulation in the Indian Ocean region, suggesting a connection between Kanem and East or Northeast Africa. In light of the finds from Kanem, a trade route along the savanna belt seems more plausible than a trans-Saharan route, especially when other glass bead finds from the continent are taken into account as well.</t>
         </is>
       </c>
     </row>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3600" yWindow="3600" windowWidth="17280" windowHeight="9984" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="FANT26 merged" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,12 +16,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -42,17 +50,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -415,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -1188,6 +1199,7 @@
           <t>Goethe Universität Frankfurt</t>
         </is>
       </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>English</t>
@@ -1240,6 +1252,7 @@
           <t>Goethe Universität Frankfurt</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>English</t>
@@ -1329,6 +1342,7 @@
           <t>Goethe Universität Frankfurt</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Deutsch</t>
@@ -1376,6 +1390,7 @@
           <t>Goethe Universität Frankfurt</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>English</t>
@@ -1402,7 +1417,92 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sainsbury Research Unit, University of East Anglia, UK</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Adding value to medieval ceramic collections from Sudan held in German museum collections</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Ahmed Adam</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Anne Haour</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>collection, medieval, ceramics, Sudan</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>As part of an ongoing move of the well-known African archaeology collections held at the University of Cologne's Forschungsstelle Afrika at Jennerstraße, we have been foregrounding the medieval ceramic collections from Sudan. These form part of the important assemblages built up during major international research projects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Schulze</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Maximilian</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Master-Student:in</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Goethe Universität Frankfurt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A9F131-F52E-4072-97BD-8EE593A4D833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCAE054-BABF-4364-B490-C031A14274F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="3600" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FANT26 merged" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="151">
   <si>
     <t>Zeitstempel</t>
   </si>
@@ -439,16 +438,63 @@
   </si>
   <si>
     <t>glass, beads, Kanem, archaeometry</t>
+  </si>
+  <si>
+    <t>Gestrich@em.uni-frankfurt.de</t>
+  </si>
+  <si>
+    <t>Puerta-Schardt@em.uni-frankfurt.de</t>
+  </si>
+  <si>
+    <t>a.hoehn@em.uni-frankfurt.de</t>
+  </si>
+  <si>
+    <t>s.magnavita@em.uni-frankfurt.de</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>ahmed.adam@uea.ac.uk</t>
+  </si>
+  <si>
+    <t>Adding value to medieval ceramic collections from Sudan held in German museum collections</t>
+  </si>
+  <si>
+    <t>Ahmed Adam</t>
+  </si>
+  <si>
+    <t>As part of an ongoing move of the well-known African archaeology collections held at the University of Cologne's Forschungsstelle Afrika at Jennerstraße, we have been foregrounding the medieval ceramic collections from Sudan. These form part of the important assemblages built up during major international research projects.</t>
+  </si>
+  <si>
+    <t>collection, medieval, ceramics, Sudan</t>
+  </si>
+  <si>
+    <t>Schulze</t>
+  </si>
+  <si>
+    <t>Maximilian</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -471,16 +517,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -781,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1280,6 +1329,9 @@
       <c r="E13" t="s">
         <v>76</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="G13" t="s">
         <v>20</v>
       </c>
@@ -1312,6 +1364,9 @@
       <c r="E14" t="s">
         <v>76</v>
       </c>
+      <c r="F14" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="G14" t="s">
         <v>20</v>
       </c>
@@ -1367,6 +1422,9 @@
       <c r="E16" t="s">
         <v>76</v>
       </c>
+      <c r="F16" t="s">
+        <v>140</v>
+      </c>
       <c r="G16" t="s">
         <v>78</v>
       </c>
@@ -1396,6 +1454,9 @@
       <c r="E17" t="s">
         <v>76</v>
       </c>
+      <c r="F17" t="s">
+        <v>141</v>
+      </c>
       <c r="G17" t="s">
         <v>20</v>
       </c>
@@ -1412,8 +1473,65 @@
         <v>136</v>
       </c>
     </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" t="s">
+        <v>146</v>
+      </c>
+      <c r="P18" t="s">
+        <v>23</v>
+      </c>
+      <c r="R18" t="s">
+        <v>148</v>
+      </c>
+      <c r="S18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F13" r:id="rId1" xr:uid="{BDF60B1C-FC69-4D79-A125-A7902011DB3F}"/>
+    <hyperlink ref="F14" r:id="rId2" xr:uid="{F2EF18AE-91A5-4B0E-B793-03470AFE866B}"/>
+    <hyperlink ref="F18" r:id="rId3" xr:uid="{A06B08F9-4DA8-4915-BF0E-BF6A156E7E93}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\FANT_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCAE054-BABF-4364-B490-C031A14274F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2833A93A-D178-4557-8F55-B7F518492C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="152">
   <si>
     <t>Zeitstempel</t>
   </si>
@@ -477,6 +477,9 @@
   </si>
   <si>
     <t>Maximilian</t>
+  </si>
+  <si>
+    <t>Maximilian_schulze97@t-online.de</t>
   </si>
 </sst>
 </file>
@@ -1524,6 +1527,9 @@
       <c r="E19" t="s">
         <v>76</v>
       </c>
+      <c r="F19" t="s">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/FANT26_merged.xlsx
+++ b/data/FANT26_merged.xlsx
@@ -1496,6 +1496,7 @@
           <t>Goethe Universität Frankfurt</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
